--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.38223999582572</v>
+        <v>2.82461399932168</v>
       </c>
       <c r="D2" t="n">
-        <v>17.57414612600209</v>
+        <v>2.85579874547534</v>
       </c>
       <c r="E2" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F2" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.833333333333343</v>
+        <v>0.2979166666666682</v>
       </c>
       <c r="D3" t="n">
-        <v>1.234732286780585</v>
+        <v>0.2006439966018451</v>
       </c>
       <c r="E3" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F3" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.42963356191518</v>
+        <v>1.694815453811217</v>
       </c>
       <c r="D4" t="n">
-        <v>10.30877049449663</v>
+        <v>1.675175205355702</v>
       </c>
       <c r="E4" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F4" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.31845107276023</v>
+        <v>2.001748299323538</v>
       </c>
       <c r="D5" t="n">
-        <v>11.95390054011969</v>
+        <v>1.94250883776945</v>
       </c>
       <c r="E5" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F5" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.50060081496646</v>
+        <v>2.51884763243205</v>
       </c>
       <c r="D6" t="n">
-        <v>15.45096872822293</v>
+        <v>2.510782418336226</v>
       </c>
       <c r="E6" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F6" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.481422895690983</v>
+        <v>1.053231220549785</v>
       </c>
       <c r="D7" t="n">
-        <v>6.450643072690482</v>
+        <v>1.048229499312203</v>
       </c>
       <c r="E7" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F7" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.850837900487943</v>
+        <v>0.9507611588292908</v>
       </c>
       <c r="D8" t="n">
-        <v>6.037179048545561</v>
+        <v>0.9810415953886537</v>
       </c>
       <c r="E8" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F8" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.82771212846675</v>
+        <v>2.897003220875848</v>
       </c>
       <c r="D9" t="n">
-        <v>18.00589360430742</v>
+        <v>2.925957710699955</v>
       </c>
       <c r="E9" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F9" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.75345479786812</v>
+        <v>6.947436404653569</v>
       </c>
       <c r="D10" t="n">
-        <v>42.54703279900961</v>
+        <v>6.913892829839062</v>
       </c>
       <c r="E10" t="n">
-        <v>11.25223577798175</v>
+        <v>1.828488313922034</v>
       </c>
       <c r="F10" t="n">
-        <v>11.28229881157891</v>
+        <v>1.833373556881572</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
